--- a/evaluation/sheets/Step14_Cityscapes_bootstrap_FD.xlsx
+++ b/evaluation/sheets/Step14_Cityscapes_bootstrap_FD.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,16 +481,16 @@
         <v>754.03317</v>
       </c>
       <c r="C2" t="n">
-        <v>815.8816509361318</v>
+        <v>815.6650031445884</v>
       </c>
       <c r="D2" t="n">
-        <v>9.712767459376263</v>
+        <v>7.726365459672138</v>
       </c>
       <c r="E2" t="n">
-        <v>797.7678314616921</v>
+        <v>801.3656603874223</v>
       </c>
       <c r="F2" t="n">
-        <v>834.4381529306316</v>
+        <v>831.1700384373125</v>
       </c>
       <c r="G2" t="n">
         <v>3000</v>
@@ -512,16 +512,16 @@
         <v>490.96475</v>
       </c>
       <c r="C3" t="n">
-        <v>552.8669497085824</v>
+        <v>551.5061347814898</v>
       </c>
       <c r="D3" t="n">
-        <v>6.988718105146094</v>
+        <v>6.746287696182115</v>
       </c>
       <c r="E3" t="n">
-        <v>540.8650794418689</v>
+        <v>538.5552663288656</v>
       </c>
       <c r="F3" t="n">
-        <v>566.6648462719651</v>
+        <v>563.505201339549</v>
       </c>
       <c r="G3" t="n">
         <v>3000</v>
@@ -543,16 +543,16 @@
         <v>494.81875</v>
       </c>
       <c r="C4" t="n">
-        <v>556.8980290488745</v>
+        <v>556.3444914265567</v>
       </c>
       <c r="D4" t="n">
-        <v>7.089877329260348</v>
+        <v>6.868414631493829</v>
       </c>
       <c r="E4" t="n">
-        <v>545.5286152449202</v>
+        <v>544.6591922336323</v>
       </c>
       <c r="F4" t="n">
-        <v>572.0557344294477</v>
+        <v>568.3312526180141</v>
       </c>
       <c r="G4" t="n">
         <v>3000</v>
@@ -574,16 +574,16 @@
         <v>509.03371</v>
       </c>
       <c r="C5" t="n">
-        <v>571.4141950987163</v>
+        <v>570.7890194793624</v>
       </c>
       <c r="D5" t="n">
-        <v>7.381092568191352</v>
+        <v>7.027283969941966</v>
       </c>
       <c r="E5" t="n">
-        <v>556.6462738352119</v>
+        <v>557.0909491262879</v>
       </c>
       <c r="F5" t="n">
-        <v>585.2402040162358</v>
+        <v>584.9973844730357</v>
       </c>
       <c r="G5" t="n">
         <v>3000</v>
@@ -605,16 +605,16 @@
         <v>543.95227</v>
       </c>
       <c r="C6" t="n">
-        <v>606.1207324967386</v>
+        <v>606.4452917067077</v>
       </c>
       <c r="D6" t="n">
-        <v>8.020002424968473</v>
+        <v>6.628852132468342</v>
       </c>
       <c r="E6" t="n">
-        <v>590.9804883687597</v>
+        <v>592.4419961175676</v>
       </c>
       <c r="F6" t="n">
-        <v>621.8374295045496</v>
+        <v>619.7085917842531</v>
       </c>
       <c r="G6" t="n">
         <v>3000</v>
@@ -636,16 +636,16 @@
         <v>541.72022</v>
       </c>
       <c r="C7" t="n">
-        <v>603.8577366905038</v>
+        <v>603.9112434301298</v>
       </c>
       <c r="D7" t="n">
-        <v>7.504037958355465</v>
+        <v>7.710715073012218</v>
       </c>
       <c r="E7" t="n">
-        <v>589.2357134568701</v>
+        <v>587.949572214724</v>
       </c>
       <c r="F7" t="n">
-        <v>617.6222237415118</v>
+        <v>617.7337465602161</v>
       </c>
       <c r="G7" t="n">
         <v>3000</v>
@@ -667,16 +667,16 @@
         <v>552.54017</v>
       </c>
       <c r="C8" t="n">
-        <v>615.8980947661325</v>
+        <v>616.323625771551</v>
       </c>
       <c r="D8" t="n">
-        <v>7.858190240067238</v>
+        <v>7.475788170511026</v>
       </c>
       <c r="E8" t="n">
-        <v>601.6079286690443</v>
+        <v>602.1403578546409</v>
       </c>
       <c r="F8" t="n">
-        <v>631.5990989544334</v>
+        <v>630.1690599101091</v>
       </c>
       <c r="G8" t="n">
         <v>3000</v>
@@ -698,16 +698,16 @@
         <v>712.69508</v>
       </c>
       <c r="C9" t="n">
-        <v>776.1614998717353</v>
+        <v>775.2033474564113</v>
       </c>
       <c r="D9" t="n">
-        <v>8.907522842512472</v>
+        <v>8.850341308903136</v>
       </c>
       <c r="E9" t="n">
-        <v>759.0492750112757</v>
+        <v>758.6961544673677</v>
       </c>
       <c r="F9" t="n">
-        <v>793.4006318219477</v>
+        <v>792.9522566149674</v>
       </c>
       <c r="G9" t="n">
         <v>3000</v>
@@ -729,16 +729,16 @@
         <v>529.61548</v>
       </c>
       <c r="C10" t="n">
-        <v>592.7270193688264</v>
+        <v>593.0603816838309</v>
       </c>
       <c r="D10" t="n">
-        <v>7.49582051993092</v>
+        <v>7.901607752040889</v>
       </c>
       <c r="E10" t="n">
-        <v>579.9400467226374</v>
+        <v>578.500568964213</v>
       </c>
       <c r="F10" t="n">
-        <v>606.9614779995591</v>
+        <v>608.8595741110777</v>
       </c>
       <c r="G10" t="n">
         <v>3000</v>
@@ -760,16 +760,16 @@
         <v>738.86826</v>
       </c>
       <c r="C11" t="n">
-        <v>802.9191403242222</v>
+        <v>801.7756774279164</v>
       </c>
       <c r="D11" t="n">
-        <v>8.577984441366201</v>
+        <v>9.265827224915389</v>
       </c>
       <c r="E11" t="n">
-        <v>784.9973332713063</v>
+        <v>783.1023379793455</v>
       </c>
       <c r="F11" t="n">
-        <v>818.5818983260948</v>
+        <v>819.4038688620742</v>
       </c>
       <c r="G11" t="n">
         <v>3000</v>
@@ -791,16 +791,16 @@
         <v>563.8459800000001</v>
       </c>
       <c r="C12" t="n">
-        <v>626.3267861032965</v>
+        <v>626.4832995494575</v>
       </c>
       <c r="D12" t="n">
-        <v>7.283453678244469</v>
+        <v>7.908718659166341</v>
       </c>
       <c r="E12" t="n">
-        <v>612.0071969927022</v>
+        <v>610.5719551879909</v>
       </c>
       <c r="F12" t="n">
-        <v>641.6809664172014</v>
+        <v>641.1053382805932</v>
       </c>
       <c r="G12" t="n">
         <v>3000</v>
@@ -822,16 +822,16 @@
         <v>505.05295</v>
       </c>
       <c r="C13" t="n">
-        <v>567.1426899882576</v>
+        <v>566.4766006418929</v>
       </c>
       <c r="D13" t="n">
-        <v>7.81025730653255</v>
+        <v>6.889090933914733</v>
       </c>
       <c r="E13" t="n">
-        <v>552.5528818237618</v>
+        <v>554.741238618088</v>
       </c>
       <c r="F13" t="n">
-        <v>582.1029381367285</v>
+        <v>580.9922009914401</v>
       </c>
       <c r="G13" t="n">
         <v>3000</v>
@@ -853,16 +853,16 @@
         <v>775.95739</v>
       </c>
       <c r="C14" t="n">
-        <v>836.9674439134964</v>
+        <v>837.954629418315</v>
       </c>
       <c r="D14" t="n">
-        <v>9.825180566182874</v>
+        <v>8.279525932179771</v>
       </c>
       <c r="E14" t="n">
-        <v>817.2864343978464</v>
+        <v>821.5109611148442</v>
       </c>
       <c r="F14" t="n">
-        <v>855.0194630368553</v>
+        <v>853.0703476715689</v>
       </c>
       <c r="G14" t="n">
         <v>3000</v>
@@ -884,16 +884,16 @@
         <v>762.84276</v>
       </c>
       <c r="C15" t="n">
-        <v>824.7708175433503</v>
+        <v>826.07795303905</v>
       </c>
       <c r="D15" t="n">
-        <v>10.8122769396473</v>
+        <v>9.553718662249029</v>
       </c>
       <c r="E15" t="n">
-        <v>804.7549542496378</v>
+        <v>806.8660001862513</v>
       </c>
       <c r="F15" t="n">
-        <v>845.3888092642528</v>
+        <v>843.0596580553851</v>
       </c>
       <c r="G15" t="n">
         <v>3000</v>
@@ -915,16 +915,16 @@
         <v>531.09065</v>
       </c>
       <c r="C16" t="n">
-        <v>593.8933679155059</v>
+        <v>593.8931097431367</v>
       </c>
       <c r="D16" t="n">
-        <v>7.560341056311183</v>
+        <v>7.248121565588186</v>
       </c>
       <c r="E16" t="n">
-        <v>578.9465717961394</v>
+        <v>578.463083896154</v>
       </c>
       <c r="F16" t="n">
-        <v>606.6096274656535</v>
+        <v>608.4133969707515</v>
       </c>
       <c r="G16" t="n">
         <v>3000</v>
@@ -946,16 +946,16 @@
         <v>526.89375</v>
       </c>
       <c r="C17" t="n">
-        <v>589.3136457848823</v>
+        <v>589.3284703996878</v>
       </c>
       <c r="D17" t="n">
-        <v>7.140649055115577</v>
+        <v>6.257006953589451</v>
       </c>
       <c r="E17" t="n">
-        <v>576.5277001013883</v>
+        <v>576.5927444702209</v>
       </c>
       <c r="F17" t="n">
-        <v>603.5966917675767</v>
+        <v>600.4577081700913</v>
       </c>
       <c r="G17" t="n">
         <v>3000</v>
@@ -977,16 +977,16 @@
         <v>546.82082</v>
       </c>
       <c r="C18" t="n">
-        <v>608.8304202512245</v>
+        <v>608.7274100731375</v>
       </c>
       <c r="D18" t="n">
-        <v>7.683216296386592</v>
+        <v>7.45986535120468</v>
       </c>
       <c r="E18" t="n">
-        <v>594.223756034106</v>
+        <v>595.9926208018194</v>
       </c>
       <c r="F18" t="n">
-        <v>624.4614680094659</v>
+        <v>623.3427035534538</v>
       </c>
       <c r="G18" t="n">
         <v>3000</v>
@@ -1008,16 +1008,16 @@
         <v>528.45798</v>
       </c>
       <c r="C19" t="n">
-        <v>590.7785458073213</v>
+        <v>590.8199259772969</v>
       </c>
       <c r="D19" t="n">
-        <v>7.884441675312179</v>
+        <v>7.121976003453917</v>
       </c>
       <c r="E19" t="n">
-        <v>576.0736754360635</v>
+        <v>577.7401139883771</v>
       </c>
       <c r="F19" t="n">
-        <v>607.6976855963113</v>
+        <v>604.6102820548315</v>
       </c>
       <c r="G19" t="n">
         <v>3000</v>
@@ -1039,16 +1039,16 @@
         <v>516.08928</v>
       </c>
       <c r="C20" t="n">
-        <v>576.8397151353092</v>
+        <v>577.3172361673898</v>
       </c>
       <c r="D20" t="n">
-        <v>7.510839224539132</v>
+        <v>7.612767866323673</v>
       </c>
       <c r="E20" t="n">
-        <v>563.3607010047924</v>
+        <v>561.9264383071306</v>
       </c>
       <c r="F20" t="n">
-        <v>593.6565597630103</v>
+        <v>590.4993204087123</v>
       </c>
       <c r="G20" t="n">
         <v>3000</v>
@@ -1070,16 +1070,16 @@
         <v>529.95214</v>
       </c>
       <c r="C21" t="n">
-        <v>592.8049869341714</v>
+        <v>593.1327197824271</v>
       </c>
       <c r="D21" t="n">
-        <v>7.715533289979881</v>
+        <v>7.411365530880723</v>
       </c>
       <c r="E21" t="n">
-        <v>578.4005932518327</v>
+        <v>579.5757508444425</v>
       </c>
       <c r="F21" t="n">
-        <v>607.3630842633074</v>
+        <v>607.5730358958042</v>
       </c>
       <c r="G21" t="n">
         <v>3000</v>
@@ -1101,16 +1101,16 @@
         <v>517.86438</v>
       </c>
       <c r="C22" t="n">
-        <v>580.1480547357647</v>
+        <v>580.1481487173788</v>
       </c>
       <c r="D22" t="n">
-        <v>7.552246475661658</v>
+        <v>7.948790623899046</v>
       </c>
       <c r="E22" t="n">
-        <v>566.4616463132304</v>
+        <v>564.9104902198177</v>
       </c>
       <c r="F22" t="n">
-        <v>594.4698377258471</v>
+        <v>595.9829929340483</v>
       </c>
       <c r="G22" t="n">
         <v>3000</v>
@@ -1132,16 +1132,16 @@
         <v>771.42574</v>
       </c>
       <c r="C23" t="n">
-        <v>834.1056502728144</v>
+        <v>833.5942806397786</v>
       </c>
       <c r="D23" t="n">
-        <v>9.616341847315379</v>
+        <v>9.127262496701073</v>
       </c>
       <c r="E23" t="n">
-        <v>815.362092648424</v>
+        <v>816.1158422878754</v>
       </c>
       <c r="F23" t="n">
-        <v>851.3228636916551</v>
+        <v>849.9137564083505</v>
       </c>
       <c r="G23" t="n">
         <v>3000</v>
@@ -1163,16 +1163,16 @@
         <v>742.5165</v>
       </c>
       <c r="C24" t="n">
-        <v>806.139872162994</v>
+        <v>806.3064822514908</v>
       </c>
       <c r="D24" t="n">
-        <v>9.519957359522747</v>
+        <v>9.806537417502424</v>
       </c>
       <c r="E24" t="n">
-        <v>788.2336053622976</v>
+        <v>788.1032280340903</v>
       </c>
       <c r="F24" t="n">
-        <v>825.4469409713183</v>
+        <v>824.0369384083211</v>
       </c>
       <c r="G24" t="n">
         <v>3000</v>
@@ -1181,6 +1181,99 @@
         <v>3000</v>
       </c>
       <c r="I24" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>730.44003</v>
+      </c>
+      <c r="C25" t="n">
+        <v>790.8322812001976</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.165989730403914</v>
+      </c>
+      <c r="E25" t="n">
+        <v>777.8960343150272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>805.4238588908865</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg20</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>798.02308</v>
+      </c>
+      <c r="C26" t="n">
+        <v>857.521345017924</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.885953912727206</v>
+      </c>
+      <c r="E26" t="n">
+        <v>841.0216478826558</v>
+      </c>
+      <c r="F26" t="n">
+        <v>872.0112175399802</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_nocfg</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>784.04614</v>
+      </c>
+      <c r="C27" t="n">
+        <v>845.1555234173816</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7.474466230592023</v>
+      </c>
+      <c r="E27" t="n">
+        <v>828.8146950619864</v>
+      </c>
+      <c r="F27" t="n">
+        <v>859.9860248172607</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I27" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1195,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,13 +1343,13 @@
         <v>-244.9994600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>-244.4674558374155</v>
+        <v>-244.875983665226</v>
       </c>
       <c r="E2" t="n">
-        <v>-260.5395538962961</v>
+        <v>-260.3812314969851</v>
       </c>
       <c r="F2" t="n">
-        <v>-227.7128732959944</v>
+        <v>-228.9934035852495</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1277,13 +1370,13 @@
         <v>18.06896</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54724539013387</v>
+        <v>19.28288469787261</v>
       </c>
       <c r="E3" t="n">
-        <v>5.446815034376289</v>
+        <v>7.138299248617625</v>
       </c>
       <c r="F3" t="n">
-        <v>31.4698721084516</v>
+        <v>30.96246480998827</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1304,16 +1397,16 @@
         <v>14.21495999999996</v>
       </c>
       <c r="D4" t="n">
-        <v>14.51616604984184</v>
+        <v>14.44452805280575</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4113172765207426</v>
+        <v>3.170130283137974</v>
       </c>
       <c r="F4" t="n">
-        <v>28.7471145524353</v>
+        <v>28.94903839134937</v>
       </c>
       <c r="G4" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
@@ -1331,13 +1424,13 @@
         <v>-34.91856000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>-34.70653739802242</v>
+        <v>-35.65627222734526</v>
       </c>
       <c r="E5" t="n">
-        <v>-50.33089954867122</v>
+        <v>-51.66343849356669</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.31729279342526</v>
+        <v>-20.71128436152334</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1358,13 +1451,13 @@
         <v>-32.68651000000006</v>
       </c>
       <c r="D6" t="n">
-        <v>-32.44354159178756</v>
+        <v>-33.12222395076744</v>
       </c>
       <c r="E6" t="n">
-        <v>-46.14681017279661</v>
+        <v>-47.82774174997072</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.87720580453096</v>
+        <v>-19.59373902168885</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1385,13 +1478,13 @@
         <v>-43.50646</v>
       </c>
       <c r="D7" t="n">
-        <v>-44.48389966741619</v>
+        <v>-45.53460629218851</v>
       </c>
       <c r="E7" t="n">
-        <v>-58.43057692533375</v>
+        <v>-58.38331238878654</v>
       </c>
       <c r="F7" t="n">
-        <v>-29.50321420632931</v>
+        <v>-30.70810034648947</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1412,13 +1505,13 @@
         <v>-203.66137</v>
       </c>
       <c r="D8" t="n">
-        <v>-204.7473047730191</v>
+        <v>-204.4143279770488</v>
       </c>
       <c r="E8" t="n">
-        <v>-221.7379188479625</v>
+        <v>-221.4611292841937</v>
       </c>
       <c r="F8" t="n">
-        <v>-187.4960052123578</v>
+        <v>-188.8141269473359</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1439,13 +1532,13 @@
         <v>-20.58177000000006</v>
       </c>
       <c r="D9" t="n">
-        <v>-21.31282427011008</v>
+        <v>-22.27136220446847</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.3020885507426</v>
+        <v>-37.06070699444873</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.25353773415952</v>
+        <v>-9.730163386416185</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1466,13 +1559,13 @@
         <v>-229.83455</v>
       </c>
       <c r="D10" t="n">
-        <v>-231.5049452255059</v>
+        <v>-230.986657948554</v>
       </c>
       <c r="E10" t="n">
-        <v>-247.3175557002131</v>
+        <v>-246.7435116841087</v>
       </c>
       <c r="F10" t="n">
-        <v>-213.4755405098261</v>
+        <v>-212.6751323102164</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1493,13 +1586,13 @@
         <v>-54.81227000000007</v>
       </c>
       <c r="D11" t="n">
-        <v>-54.91259100458029</v>
+        <v>-55.69428007009505</v>
       </c>
       <c r="E11" t="n">
-        <v>-68.46563106544484</v>
+        <v>-67.29033059231611</v>
       </c>
       <c r="F11" t="n">
-        <v>-39.85870209663879</v>
+        <v>-39.30141136044995</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1520,16 +1613,16 @@
         <v>3.980759999999975</v>
       </c>
       <c r="D12" t="n">
-        <v>4.271505110458695</v>
+        <v>4.312418837469561</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.15755989584338</v>
+        <v>-8.721925775095121</v>
       </c>
       <c r="F12" t="n">
-        <v>19.8257303337578</v>
+        <v>14.87708822208918</v>
       </c>
       <c r="G12" t="n">
-        <v>0.315</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="13">
@@ -1547,13 +1640,13 @@
         <v>-266.92368</v>
       </c>
       <c r="D13" t="n">
-        <v>-265.5532488147801</v>
+        <v>-267.1656099389527</v>
       </c>
       <c r="E13" t="n">
-        <v>-285.1667995353612</v>
+        <v>-281.9228919714488</v>
       </c>
       <c r="F13" t="n">
-        <v>-248.3950495945868</v>
+        <v>-250.2621157640145</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1574,13 +1667,13 @@
         <v>-253.80905</v>
       </c>
       <c r="D14" t="n">
-        <v>-253.3566224446339</v>
+        <v>-255.2889335596876</v>
       </c>
       <c r="E14" t="n">
-        <v>-270.0508139681843</v>
+        <v>-274.9898860327143</v>
       </c>
       <c r="F14" t="n">
-        <v>-234.8147273989953</v>
+        <v>-237.7787860358708</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1601,10 +1694,10 @@
         <v>-22.05694</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.47917281678972</v>
+        <v>-23.1040902637743</v>
       </c>
       <c r="E15" t="n">
-        <v>-36.57455292270104</v>
+        <v>-34.09334133391726</v>
       </c>
       <c r="F15" t="n">
         <v>-8.798474579726415</v>
@@ -1628,13 +1721,13 @@
         <v>-17.86003999999997</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.89945068616593</v>
+        <v>-18.5394509203254</v>
       </c>
       <c r="E16" t="n">
-        <v>-31.22033431610687</v>
+        <v>-30.25874948909006</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.458784654886649</v>
+        <v>-5.957750848464965</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1655,13 +1748,13 @@
         <v>-37.78711000000004</v>
       </c>
       <c r="D17" t="n">
-        <v>-37.41622515250823</v>
+        <v>-37.93839059377521</v>
       </c>
       <c r="E17" t="n">
-        <v>-51.01379266744741</v>
+        <v>-51.0054705170618</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.96980172101993</v>
+        <v>-26.531391825678</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1682,16 +1775,16 @@
         <v>-19.42427000000004</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.36435070860501</v>
+        <v>-20.03090649793435</v>
       </c>
       <c r="E18" t="n">
-        <v>-32.53086589929412</v>
+        <v>-33.15444138971556</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.033450494157563</v>
+        <v>-6.661717821777501</v>
       </c>
       <c r="G18" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1709,16 +1802,16 @@
         <v>-7.055570000000046</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.425520036593025</v>
+        <v>-6.528216688027408</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.26601388321492</v>
+        <v>-21.08009284043254</v>
       </c>
       <c r="F19" t="n">
-        <v>9.382813133633878</v>
+        <v>8.930414139703409</v>
       </c>
       <c r="G19" t="n">
-        <v>0.755</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -1736,13 +1829,13 @@
         <v>-20.91843</v>
       </c>
       <c r="D20" t="n">
-        <v>-21.39079183545514</v>
+        <v>-22.34370030306473</v>
       </c>
       <c r="E20" t="n">
-        <v>-35.12444073103104</v>
+        <v>-36.10350821611367</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.107468051046361</v>
+        <v>-9.202226124228888</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1763,16 +1856,16 @@
         <v>-8.830669999999998</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.733859637048436</v>
+        <v>-9.359129238016333</v>
       </c>
       <c r="E21" t="n">
-        <v>-21.67881088894651</v>
+        <v>-23.18241854120233</v>
       </c>
       <c r="F21" t="n">
-        <v>5.563798074662454</v>
+        <v>3.898606365944994</v>
       </c>
       <c r="G21" t="n">
-        <v>0.88</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="22">
@@ -1790,13 +1883,13 @@
         <v>-262.39203</v>
       </c>
       <c r="D22" t="n">
-        <v>-262.6914551740981</v>
+        <v>-262.8052611604161</v>
       </c>
       <c r="E22" t="n">
-        <v>-279.4077417648239</v>
+        <v>-278.2829221593096</v>
       </c>
       <c r="F22" t="n">
-        <v>-244.0661157639402</v>
+        <v>-243.9955638045594</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1817,15 +1910,96 @@
         <v>-233.48279</v>
       </c>
       <c r="D23" t="n">
-        <v>-234.7256770642778</v>
+        <v>-235.5174627721285</v>
       </c>
       <c r="E23" t="n">
-        <v>-253.4117689912232</v>
+        <v>-252.6697096659039</v>
       </c>
       <c r="F23" t="n">
-        <v>-214.8891659992202</v>
+        <v>-218.3280513819796</v>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_mask_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-221.40632</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-220.0432617208352</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-233.8903668449265</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-205.5544540197778</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_mask_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_cfg20</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-288.9893700000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-286.7323255385616</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-302.3431318174844</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-271.877320377383</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_mask_ema200000_n3000_r500_colsample_anc500_cfg15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cityscapes_fdgan_wideband35_ema200000_n3000_r500_colsample_anc500_nocfg</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-275.0124300000001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-274.3665039380192</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-287.6759581810664</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-257.3710135886801</v>
+      </c>
+      <c r="G26" t="n">
         <v>1</v>
       </c>
     </row>
